--- a/data/trans_dic/P36$pan-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P36$pan-Provincia-trans_dic.xlsx
@@ -524,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que desayuna, al menos, pan, tostadas, galletas, cereales, bollería, ...</t>
+          <t>Población que desayuna, al menos, pan, tostadas, galletas, cereales, bollería, ... (tasa de respuesta: 99,85%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>64,94; 75,71</t>
+          <t>64,95; 75,96</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>63,27; 74,99</t>
+          <t>64,36; 75,07</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>75,63; 84,98</t>
+          <t>75,46; 85,19</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>57,22; 69,59</t>
+          <t>56,7; 69,57</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>68,9; 80,12</t>
+          <t>68,64; 79,77</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>74,75; 83,91</t>
+          <t>75,2; 84,29</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>63,21; 71,13</t>
+          <t>62,64; 70,94</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>68,2; 75,94</t>
+          <t>68,28; 76,07</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>76,56; 83,37</t>
+          <t>76,76; 83,15</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>76,76; 83,95</t>
+          <t>76,56; 84,1</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>76,35; 83,59</t>
+          <t>75,81; 83,19</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>83,82; 89,79</t>
+          <t>83,65; 89,66</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>82,46; 88,47</t>
+          <t>82,26; 88,4</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>83,41; 89,66</t>
+          <t>83,51; 89,58</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>89,2; 94,07</t>
+          <t>88,99; 93,88</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>80,6; 85,19</t>
+          <t>80,89; 85,59</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>80,81; 85,56</t>
+          <t>80,57; 85,98</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>87,52; 91,36</t>
+          <t>87,66; 91,37</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>80,83; 88,35</t>
+          <t>80,32; 88,14</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>77,66; 85,79</t>
+          <t>77,26; 85,67</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>79,96; 87,63</t>
+          <t>80,11; 88,21</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>80,34; 88,17</t>
+          <t>80,5; 87,98</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>76,69; 85,12</t>
+          <t>76,5; 84,93</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>82,17; 89,69</t>
+          <t>81,74; 89,1</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>81,45; 87,31</t>
+          <t>81,79; 87,28</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>78,48; 84,49</t>
+          <t>78,65; 84,64</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>82,1; 87,84</t>
+          <t>82,07; 87,52</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>62,75; 72,49</t>
+          <t>62,94; 72,56</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>74,89; 83,34</t>
+          <t>74,92; 83,69</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>73,43; 82,42</t>
+          <t>73,59; 82,75</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>65,5; 74,79</t>
+          <t>65,28; 75,1</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>81,21; 88,51</t>
+          <t>81,12; 88,5</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>80,3; 87,85</t>
+          <t>80,02; 87,49</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>66,09; 72,68</t>
+          <t>65,8; 72,34</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>79,43; 85,04</t>
+          <t>79,46; 84,93</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>78,1; 83,77</t>
+          <t>78,27; 83,98</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>57,98; 71,18</t>
+          <t>57,48; 70,76</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>65,92; 79,16</t>
+          <t>65,91; 78,44</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>87,21; 95,01</t>
+          <t>87,28; 95,11</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>63,2; 75,84</t>
+          <t>63,54; 76,48</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>78,31; 88,09</t>
+          <t>77,47; 87,84</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>83,34; 91,79</t>
+          <t>82,95; 91,88</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>62,8; 72,12</t>
+          <t>62,57; 71,87</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>73,96; 81,92</t>
+          <t>73,84; 81,63</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>86,63; 92,47</t>
+          <t>86,68; 92,52</t>
         </is>
       </c>
     </row>
@@ -1228,47 +1228,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>67,23; 77,89</t>
+          <t>67,91; 78,49</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>70,53; 81,04</t>
+          <t>70,69; 81,12</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>69,68; 80,68</t>
+          <t>70,45; 81,02</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>65,04; 75,68</t>
+          <t>64,47; 75,41</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>68,8; 79,25</t>
+          <t>68,8; 78,83</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>78,61; 87,69</t>
+          <t>78,3; 87,9</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>68,24; 75,72</t>
+          <t>66,68; 75,11</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>71,82; 78,99</t>
+          <t>71,09; 78,86</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>75,7; 83,04</t>
+          <t>76,1; 83,08</t>
         </is>
       </c>
     </row>
@@ -1338,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>73,43; 80,4</t>
+          <t>73,42; 80,53</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>73,31; 80,43</t>
+          <t>73,78; 80,88</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>79,98; 86,15</t>
+          <t>80,21; 86,23</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>73,15; 80,42</t>
+          <t>73,17; 79,99</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>74,34; 80,89</t>
+          <t>74,33; 80,8</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>85,3; 90,29</t>
+          <t>85,24; 90,26</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>74,74; 79,54</t>
+          <t>74,55; 79,46</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>75,16; 80,02</t>
+          <t>75,05; 79,76</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>83,24; 87,35</t>
+          <t>83,46; 87,45</t>
         </is>
       </c>
     </row>
@@ -1448,47 +1448,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>77,28; 82,83</t>
+          <t>77,02; 83,05</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>87,2; 91,71</t>
+          <t>87,17; 91,95</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>86,83; 91,37</t>
+          <t>87,03; 91,45</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>82,03; 87,21</t>
+          <t>81,63; 87,2</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>87,6; 91,95</t>
+          <t>87,61; 91,89</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>88,79; 92,89</t>
+          <t>88,94; 92,94</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>80,35; 84,43</t>
+          <t>80,65; 84,5</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>88,2; 91,58</t>
+          <t>88,17; 91,31</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>88,56; 91,58</t>
+          <t>88,54; 91,68</t>
         </is>
       </c>
     </row>
@@ -1558,47 +1558,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>74,98; 77,87</t>
+          <t>74,85; 77,97</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>78,62; 81,44</t>
+          <t>78,76; 81,52</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>83,13; 85,69</t>
+          <t>83,14; 85,7</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>76,77; 79,51</t>
+          <t>76,64; 79,57</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>81,58; 84,22</t>
+          <t>81,57; 84,12</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>86,45; 88,67</t>
+          <t>86,5; 88,82</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>76,3; 78,34</t>
+          <t>76,29; 78,35</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>80,67; 82,55</t>
+          <t>80,52; 82,43</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>85,23; 86,92</t>
+          <t>85,21; 86,93</t>
         </is>
       </c>
     </row>
@@ -1654,7 +1654,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que desayuna, al menos, pan, tostadas, galletas, cereales, bollería, ...</t>
+          <t>Población que desayuna, al menos, pan, tostadas, galletas, cereales, bollería, ... (tasa de respuesta: 99,85%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1861,47 +1861,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>176143; 205362</t>
+          <t>176183; 206041</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>186486; 221019</t>
+          <t>189681; 221254</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>222173; 249636</t>
+          <t>221664; 250241</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>148631; 180779</t>
+          <t>147298; 180718</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>197266; 229376</t>
+          <t>196516; 228391</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>215795; 242255</t>
+          <t>217095; 243349</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>335641; 377705</t>
+          <t>332635; 376670</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>396265; 441260</t>
+          <t>396741; 441997</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>445949; 485620</t>
+          <t>447073; 484302</t>
         </is>
       </c>
     </row>
@@ -2024,47 +2024,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>377708; 413041</t>
+          <t>376703; 413786</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>385165; 421723</t>
+          <t>382434; 419674</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>419433; 449292</t>
+          <t>418571; 448625</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>415541; 445830</t>
+          <t>414555; 445469</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>435204; 467790</t>
+          <t>435693; 467388</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>466569; 492042</t>
+          <t>465505; 491069</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>802794; 848459</t>
+          <t>805641; 852436</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>829282; 878010</t>
+          <t>826824; 882301</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>895739; 935079</t>
+          <t>897198; 935144</t>
         </is>
       </c>
     </row>
@@ -2187,47 +2187,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>257736; 281700</t>
+          <t>256089; 281026</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>250959; 277226</t>
+          <t>249634; 276838</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>254712; 279166</t>
+          <t>255191; 280994</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>269482; 295728</t>
+          <t>270011; 295084</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>261521; 290279</t>
+          <t>260881; 289644</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>276359; 301625</t>
+          <t>274897; 299666</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>532913; 571232</t>
+          <t>535117; 571040</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>521242; 561143</t>
+          <t>522367; 562153</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>537676; 575216</t>
+          <t>537473; 573118</t>
         </is>
       </c>
     </row>
@@ -2350,47 +2350,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>224460; 259292</t>
+          <t>225141; 259541</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>279255; 310756</t>
+          <t>279360; 312077</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>271653; 304930</t>
+          <t>272270; 306137</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>243292; 277795</t>
+          <t>242502; 278978</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>315855; 344258</t>
+          <t>315522; 344226</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>310981; 340228</t>
+          <t>309909; 338844</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>481909; 529954</t>
+          <t>479763; 527480</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>605170; 647852</t>
+          <t>605375; 647041</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>591383; 634350</t>
+          <t>592698; 635916</t>
         </is>
       </c>
     </row>
@@ -2513,47 +2513,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>117362; 144071</t>
+          <t>116338; 143229</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>140165; 168318</t>
+          <t>140128; 166786</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>184213; 200679</t>
+          <t>184364; 200884</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>130622; 156730</t>
+          <t>131315; 158066</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>171965; 193431</t>
+          <t>170123; 192885</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>182164; 200639</t>
+          <t>181326; 200848</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>256883; 295042</t>
+          <t>255951; 294016</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>319658; 354063</t>
+          <t>319164; 352813</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>372334; 397448</t>
+          <t>372541; 397641</t>
         </is>
       </c>
     </row>
@@ -2676,47 +2676,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>182067; 210923</t>
+          <t>183904; 212565</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>193226; 222021</t>
+          <t>193672; 222242</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>183342; 212277</t>
+          <t>185370; 213185</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>180911; 210487</t>
+          <t>179315; 209762</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>191960; 221111</t>
+          <t>191946; 219922</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>213758; 238461</t>
+          <t>212905; 239024</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>374623; 415658</t>
+          <t>366019; 412336</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>397158; 436816</t>
+          <t>393131; 436069</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>405026; 444324</t>
+          <t>407154; 444494</t>
         </is>
       </c>
     </row>
@@ -2839,47 +2839,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>450127; 492839</t>
+          <t>450085; 493621</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>485870; 533092</t>
+          <t>488978; 536045</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>523664; 564107</t>
+          <t>525190; 564637</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>465419; 511677</t>
+          <t>465560; 508957</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>515810; 561237</t>
+          <t>515724; 560618</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>587910; 622303</t>
+          <t>587538; 622071</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>933723; 993607</t>
+          <t>931359; 992696</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>1019616; 1085530</t>
+          <t>1018110; 1082077</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>1118799; 1173986</t>
+          <t>1121746; 1175371</t>
         </is>
       </c>
     </row>
@@ -3002,47 +3002,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>574810; 616070</t>
+          <t>572838; 617713</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>676909; 711920</t>
+          <t>676677; 713726</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>676051; 711411</t>
+          <t>677564; 712025</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>642738; 683334</t>
+          <t>639544; 683184</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>719818; 755602</t>
+          <t>719883; 755096</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>733564; 767453</t>
+          <t>734829; 767818</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>1227207; 1289543</t>
+          <t>1231706; 1290559</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>1409457; 1463453</t>
+          <t>1408879; 1459153</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>1421141; 1469572</t>
+          <t>1420796; 1471223</t>
         </is>
       </c>
     </row>
@@ -3165,47 +3165,47 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>2451660; 2546062</t>
+          <t>2447433; 2549606</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>2689402; 2785872</t>
+          <t>2694410; 2788728</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>2818298; 2905288</t>
+          <t>2818906; 2905461</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>2591023; 2683720</t>
+          <t>2586715; 2685599</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>2897809; 2991591</t>
+          <t>2897471; 2987930</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>3061402; 3139965</t>
+          <t>3063207; 3145274</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>5070013; 5205592</t>
+          <t>5069578; 5206523</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>5625395; 5756348</t>
+          <t>5614404; 5748032</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>5907625; 6024899</t>
+          <t>5906603; 6025465</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P36$pan-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P36$pan-Provincia-trans_dic.xlsx
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>64,95; 75,96</t>
+          <t>64,8; 75,96</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>64,36; 75,07</t>
+          <t>64,0; 75,36</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>75,46; 85,19</t>
+          <t>75,29; 84,81</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>56,7; 69,57</t>
+          <t>57,43; 69,59</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>68,64; 79,77</t>
+          <t>68,99; 79,51</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>75,2; 84,29</t>
+          <t>75,11; 84,22</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>62,64; 70,94</t>
+          <t>62,67; 71,15</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>68,28; 76,07</t>
+          <t>68,16; 75,9</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>76,76; 83,15</t>
+          <t>76,65; 83,47</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>76,56; 84,1</t>
+          <t>76,89; 83,88</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>75,81; 83,19</t>
+          <t>76,12; 83,11</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>83,65; 89,66</t>
+          <t>84,12; 89,86</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>82,26; 88,4</t>
+          <t>82,4; 88,46</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>83,51; 89,58</t>
+          <t>83,41; 89,52</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>88,99; 93,88</t>
+          <t>89,33; 94,13</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>80,89; 85,59</t>
+          <t>80,58; 85,52</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>80,57; 85,98</t>
+          <t>80,96; 85,73</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>87,66; 91,37</t>
+          <t>87,61; 91,29</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>80,32; 88,14</t>
+          <t>80,18; 88,49</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>77,26; 85,67</t>
+          <t>77,66; 85,94</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>80,11; 88,21</t>
+          <t>80,09; 87,82</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>80,5; 87,98</t>
+          <t>80,56; 88,36</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>76,5; 84,93</t>
+          <t>76,78; 85,06</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>81,74; 89,1</t>
+          <t>82,11; 89,42</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>81,79; 87,28</t>
+          <t>81,62; 87,29</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>78,65; 84,64</t>
+          <t>78,35; 84,5</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>82,07; 87,52</t>
+          <t>82,26; 87,91</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>62,94; 72,56</t>
+          <t>62,53; 72,23</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>74,92; 83,69</t>
+          <t>74,77; 83,79</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>73,59; 82,75</t>
+          <t>73,29; 82,8</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>65,28; 75,1</t>
+          <t>65,46; 75,04</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>81,12; 88,5</t>
+          <t>81,45; 88,67</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>80,02; 87,49</t>
+          <t>79,82; 87,66</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>65,8; 72,34</t>
+          <t>65,55; 72,32</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>79,46; 84,93</t>
+          <t>79,4; 84,91</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>78,27; 83,98</t>
+          <t>78,03; 83,77</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>57,48; 70,76</t>
+          <t>57,57; 70,93</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>65,91; 78,44</t>
+          <t>65,22; 78,32</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>87,28; 95,11</t>
+          <t>87,13; 94,98</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>63,54; 76,48</t>
+          <t>64,33; 76,38</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>77,47; 87,84</t>
+          <t>78,04; 88,1</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>82,95; 91,88</t>
+          <t>83,36; 91,46</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>62,57; 71,87</t>
+          <t>62,73; 71,92</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>73,84; 81,63</t>
+          <t>74,19; 82,06</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>86,68; 92,52</t>
+          <t>86,44; 92,3</t>
         </is>
       </c>
     </row>
@@ -1228,47 +1228,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>67,91; 78,49</t>
+          <t>68,06; 78,45</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>70,69; 81,12</t>
+          <t>70,95; 81,18</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>70,45; 81,02</t>
+          <t>70,24; 81,05</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>64,47; 75,41</t>
+          <t>64,79; 75,62</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>68,8; 78,83</t>
+          <t>68,53; 78,92</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>78,3; 87,9</t>
+          <t>78,62; 87,7</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>66,68; 75,11</t>
+          <t>68,3; 75,61</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>71,09; 78,86</t>
+          <t>71,58; 78,88</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>76,1; 83,08</t>
+          <t>76,28; 83,26</t>
         </is>
       </c>
     </row>
@@ -1338,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>73,42; 80,53</t>
+          <t>73,86; 80,79</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>73,78; 80,88</t>
+          <t>73,74; 80,23</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>80,21; 86,23</t>
+          <t>80,11; 86,16</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>73,17; 79,99</t>
+          <t>73,59; 80,34</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>74,33; 80,8</t>
+          <t>74,42; 80,92</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>85,24; 90,26</t>
+          <t>84,77; 90,06</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>74,55; 79,46</t>
+          <t>74,69; 79,57</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>75,05; 79,76</t>
+          <t>75,09; 79,85</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>83,46; 87,45</t>
+          <t>83,5; 87,47</t>
         </is>
       </c>
     </row>
@@ -1448,47 +1448,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>77,02; 83,05</t>
+          <t>77,06; 83,05</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>87,17; 91,95</t>
+          <t>87,46; 91,97</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>87,03; 91,45</t>
+          <t>86,91; 91,43</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>81,63; 87,2</t>
+          <t>82,14; 87,27</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>87,61; 91,89</t>
+          <t>87,6; 92,03</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>88,94; 92,94</t>
+          <t>88,73; 92,8</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>80,65; 84,5</t>
+          <t>80,48; 84,42</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>88,17; 91,31</t>
+          <t>88,15; 91,36</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>88,54; 91,68</t>
+          <t>88,67; 91,69</t>
         </is>
       </c>
     </row>
@@ -1558,47 +1558,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>74,85; 77,97</t>
+          <t>74,97; 77,83</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>78,76; 81,52</t>
+          <t>78,81; 81,67</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>83,14; 85,7</t>
+          <t>83,23; 85,62</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>76,64; 79,57</t>
+          <t>76,73; 79,51</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>81,57; 84,12</t>
+          <t>81,59; 84,13</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>86,5; 88,82</t>
+          <t>86,42; 88,65</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>76,29; 78,35</t>
+          <t>76,21; 78,31</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>80,52; 82,43</t>
+          <t>80,55; 82,46</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>85,21; 86,93</t>
+          <t>85,25; 86,85</t>
         </is>
       </c>
     </row>
@@ -1861,47 +1861,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>176183; 206041</t>
+          <t>175776; 206024</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>189681; 221254</t>
+          <t>188641; 222118</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>221664; 250241</t>
+          <t>221170; 249124</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>147298; 180718</t>
+          <t>149195; 180772</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>196516; 228391</t>
+          <t>197534; 227655</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>217095; 243349</t>
+          <t>216855; 243143</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>332635; 376670</t>
+          <t>332766; 377834</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>396741; 441997</t>
+          <t>396056; 440990</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>447073; 484302</t>
+          <t>446474; 486193</t>
         </is>
       </c>
     </row>
@@ -2024,47 +2024,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>376703; 413786</t>
+          <t>378313; 412705</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>382434; 419674</t>
+          <t>384012; 419270</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>418571; 448625</t>
+          <t>420908; 449630</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>414555; 445469</t>
+          <t>415273; 445805</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>435693; 467388</t>
+          <t>435186; 467043</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>465505; 491069</t>
+          <t>467279; 492365</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>805641; 852436</t>
+          <t>802526; 851776</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>826824; 882301</t>
+          <t>830850; 879754</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>897198; 935144</t>
+          <t>896689; 934307</t>
         </is>
       </c>
     </row>
@@ -2187,47 +2187,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>256089; 281026</t>
+          <t>255655; 282159</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>249634; 276838</t>
+          <t>250932; 277689</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>255191; 280994</t>
+          <t>255136; 279750</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>270011; 295084</t>
+          <t>270216; 296358</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>260881; 289644</t>
+          <t>261847; 290058</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>274897; 299666</t>
+          <t>276145; 300744</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>535117; 571040</t>
+          <t>534036; 571074</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>522367; 562153</t>
+          <t>520344; 561194</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>537473; 573118</t>
+          <t>538680; 575728</t>
         </is>
       </c>
     </row>
@@ -2350,47 +2350,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>225141; 259541</t>
+          <t>223652; 258373</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>279360; 312077</t>
+          <t>278817; 312442</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>272270; 306137</t>
+          <t>271161; 306333</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>242502; 278978</t>
+          <t>243169; 278749</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>315522; 344226</t>
+          <t>316814; 344882</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>309909; 338844</t>
+          <t>309127; 339492</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>479763; 527480</t>
+          <t>477989; 527325</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>605375; 647041</t>
+          <t>604933; 646901</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>592698; 635916</t>
+          <t>590899; 634359</t>
         </is>
       </c>
     </row>
@@ -2513,47 +2513,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>116338; 143229</t>
+          <t>116530; 143565</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>140128; 166786</t>
+          <t>138667; 166524</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>184364; 200884</t>
+          <t>184044; 200607</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>131315; 158066</t>
+          <t>132952; 157846</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>170123; 192885</t>
+          <t>171362; 193469</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>181326; 200848</t>
+          <t>182205; 199929</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>255951; 294016</t>
+          <t>256616; 294191</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>319164; 352813</t>
+          <t>320657; 354679</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>372541; 397641</t>
+          <t>371533; 396723</t>
         </is>
       </c>
     </row>
@@ -2676,47 +2676,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>183904; 212565</t>
+          <t>184301; 212447</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>193672; 222242</t>
+          <t>194377; 222418</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>185370; 213185</t>
+          <t>184815; 213268</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>179315; 209762</t>
+          <t>180201; 210322</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>191946; 219922</t>
+          <t>191194; 220177</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>212905; 239024</t>
+          <t>213782; 238486</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>366019; 412336</t>
+          <t>374960; 415092</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>393131; 436069</t>
+          <t>395833; 436166</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>407154; 444494</t>
+          <t>408117; 445492</t>
         </is>
       </c>
     </row>
@@ -2839,47 +2839,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>450085; 493621</t>
+          <t>452750; 495206</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>488978; 536045</t>
+          <t>488714; 531773</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>525190; 564637</t>
+          <t>524545; 564155</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>465560; 508957</t>
+          <t>468247; 511156</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>515724; 560618</t>
+          <t>516334; 561444</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>587538; 622071</t>
+          <t>584290; 620739</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>931359; 992696</t>
+          <t>933106; 994047</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>1018110; 1082077</t>
+          <t>1018662; 1083294</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>1121746; 1175371</t>
+          <t>1122190; 1175574</t>
         </is>
       </c>
     </row>
@@ -3002,47 +3002,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>572838; 617713</t>
+          <t>573143; 617709</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>676677; 713726</t>
+          <t>678877; 713929</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>677564; 712025</t>
+          <t>676680; 711897</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>639544; 683184</t>
+          <t>643605; 683797</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>719883; 755096</t>
+          <t>719827; 756276</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>734829; 767818</t>
+          <t>733096; 766699</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>1231706; 1290559</t>
+          <t>1229122; 1289329</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>1408879; 1459153</t>
+          <t>1408569; 1459913</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>1420796; 1471223</t>
+          <t>1422943; 1471395</t>
         </is>
       </c>
     </row>
@@ -3165,47 +3165,47 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>2447433; 2549606</t>
+          <t>2451542; 2544753</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>2694410; 2788728</t>
+          <t>2695955; 2793756</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>2818906; 2905461</t>
+          <t>2821863; 2902886</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>2586715; 2685599</t>
+          <t>2589879; 2683530</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>2897471; 2987930</t>
+          <t>2898251; 2988337</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>3063207; 3145274</t>
+          <t>3060392; 3139268</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>5069578; 5206523</t>
+          <t>5064353; 5203467</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>5614404; 5748032</t>
+          <t>5616549; 5749723</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>5906603; 6025465</t>
+          <t>5909064; 6020041</t>
         </is>
       </c>
     </row>
